--- a/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/continuation/conductor_1_operation.xlsx
+++ b/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/continuation/conductor_1_operation.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="4" r:id="R2919acf8a793437d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="Rec61107518354d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="Re6040dcfb3a64d51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="Rd17724f5cd1d4e06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="2" r:id="R0a41f570f9d046ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="4" r:id="R53bed82071634046"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="R6c5af66901b84685"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="R36e052f431294c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="Rf1f3fbc063984113"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="2" r:id="R6edb6f4041c7448b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -647,7 +647,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D4" s="62" t="str">
-        <x:v>flag to define initialization and the hydraulic boundary conditions (&gt;0 value from below, &lt;0 valure from input file: press.dat, temp.dat, mdot.dat). 1 = inlet and outlet pressure, inlet (outlet) temperaure; 2 = inlet pressure and temperature, outlet mass flow rate; 3 = inlet mass flow rate and temperature, outlet pressure.</x:v>
+        <x:v>Flag used to define the initialization and hydraulic boundary conditions (&gt; 0: use the values below; &lt; 0: read values from the input files press.dat, temp.dat, and mdot.dat). 1 = inlet and outlet pressure, and inlet (outlet) temperature; 2 = inlet pressure and temperature, and outlet mass flow rate; 3 = inlet mass flow rate and temperature, and outlet pressure.</x:v>
       </x:c>
       <x:c r="E4" s="61" t="n">
         <x:v>1</x:v>
@@ -787,7 +787,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="62" t="str">
-        <x:v>flag to define the flow direction. Possible values: forward or Forward or FORWARD (inlet at x  = 0 and outlet at x = L); backward or Backward or BACKWARD (inlet at x = L and outlet at x = 0). Defaults to forward. If chanels are in hydraulic parallel, they must all have the same flow direction.</x:v>
+        <x:v>Flag used to define the flow direction. Possible values: forward, Forward, or FORWARD (inlet at x = 0 and outlet at x = L); backward, Backward, or BACKWARD (inlet at x = L and outlet at x = 0). Defaults to forward. Channels in hydraulic parallel must all have the same flow direction.</x:v>
       </x:c>
       <x:c r="E11" s="61" t="str">
         <x:v>forward</x:v>
@@ -900,7 +900,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the operating current data, if IOP_MODE = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the operating-current data when IOP_MODE = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E5" s="61" t="str">
         <x:v>linear</x:v>
@@ -917,7 +917,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D6" s="62" t="str">
-        <x:v>Flag to allow user to specify the potential value in some axial location of the conductor. Possible values: 1 = user can assign the position and the value of the potential; 0 = user can not assign these values. Defaults to 0</x:v>
+        <x:v>Flag used to allow the user to specify potential values at selected axial locations of the conductor. Possible values: 1 = the user can assign the locations and potential values; 0 = the user cannot assign these values. Defaults to 0.</x:v>
       </x:c>
       <x:c r="E6" s="78" t="n">
         <x:v>1</x:v>
@@ -951,7 +951,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D8" s="62" t="str">
-        <x:v>List of axial coordinate at which assing the fix potential value, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if at z = 0.5m z = 1.0m and z = 1.5m user wants to fix the potential value, write 0.5,1.0,1.5.</x:v>
+        <x:v>List of axial coordinates at which the fixed potential values are assigned, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to fix the potential at z = 0.5 m, 1.0 m, and 1.5 m, enter 0.5,1.0,1.5.</x:v>
       </x:c>
       <x:c r="E8" s="61" t="n">
         <x:v>0</x:v>
@@ -968,7 +968,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D9" s="62" t="str">
-        <x:v>List of fix potential value the user wants to assig, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if user wants to assign three potential values, write: 0.0,2.0,4.0.</x:v>
+        <x:v>List of fixed potential values, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to assign three potential values, enter 0.0,2.0,4.0.</x:v>
       </x:c>
       <x:c r="E9" s="61" t="n">
         <x:v>0</x:v>
@@ -1002,7 +1002,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field data, if IBFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field data when IBIFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E11" s="61" t="str">
         <x:v>linear</x:v>
@@ -1036,7 +1036,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D13" s="62" t="str">
-        <x:v>magnetic field value at x = 0 m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = 0 m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E13" s="61" t="n">
         <x:v>17</x:v>
@@ -1053,7 +1053,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D14" s="62" t="str">
-        <x:v>magnetic field value at x = L m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = L m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E14" s="61" t="n">
         <x:v>17</x:v>
@@ -1087,7 +1087,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D16" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field gradient data, if IALPHAB = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field-gradient data when IALPHAB = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E16" s="61" t="str">
         <x:v>linear</x:v>
@@ -1172,7 +1172,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D21" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the heat data, if IQFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the heat data when IQFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E21" s="61" t="str">
         <x:v>linear</x:v>
@@ -1240,7 +1240,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D25" s="62" t="str">
-        <x:v>heating start time. Recommended: add the time at with the heating starts also if the heat is from external file, IQFUN = -1 (requested for the correct evaluation of htc between fluid and solid)</x:v>
+        <x:v>Heating start time. Specify this time even when the heat is read from an external file (IQFUN = -1); it is required for the correct evaluation of the HTC between the fluid and the solid.</x:v>
       </x:c>
       <x:c r="E25" s="61" t="n">
         <x:v>610.01</x:v>
@@ -1325,7 +1325,7 @@
         <x:v>bool</x:v>
       </x:c>
       <x:c r="D30" s="62" t="str">
-        <x:v>Flag to decide if the current sharing temperature should be evaluated at each time steps or not (improve speed). Possible values: False = evaluate the current sharing temperature only at the initialization and at the end of the simulation; True = evaluate the current sharing temperature at each time steps (affects computaion time). Defaults to False.</x:v>
+        <x:v>Flag used to determine whether the current-sharing temperature is evaluated at every time step. Possible values: False = evaluate it only during initialization and at the end of the simulation; True = evaluate it at every time step (increases computation time). Defaults to False.</x:v>
       </x:c>
       <x:c r="E30" s="79" t="b">
         <x:v>1</x:v>
@@ -1447,7 +1447,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the operating current data, if IOP_MODE = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the operating-current data when IOP_MODE = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E5" s="61" t="str">
         <x:v>linear</x:v>
@@ -1464,7 +1464,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D6" s="62" t="str">
-        <x:v>Flag to allow user to specify the potential value in some axial location of the conductor. Possible values: 1 = user can assign the position and the value of the potential; 0 = user can not assign these values. Defaults to 0</x:v>
+        <x:v>Flag used to allow the user to specify potential values at selected axial locations of the conductor. Possible values: 1 = the user can assign the locations and potential values; 0 = the user cannot assign these values. Defaults to 0.</x:v>
       </x:c>
       <x:c r="E6" s="78" t="n">
         <x:v>0</x:v>
@@ -1498,7 +1498,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D8" s="62" t="str">
-        <x:v>List of axial coordinate at which assing the fix potential value, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if at z = 0.5m z = 1.0m and z = 1.5m user wants to fix the potential value, write 0.5,1.0,1.5.</x:v>
+        <x:v>List of axial coordinates at which the fixed potential values are assigned, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to fix the potential at z = 0.5 m, 1.0 m, and 1.5 m, enter 0.5,1.0,1.5.</x:v>
       </x:c>
       <x:c r="E8" s="61" t="n">
         <x:v>0</x:v>
@@ -1515,7 +1515,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D9" s="62" t="str">
-        <x:v>List of fix potential value the user wants to assig, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if user wants to assign three potential values, write: 0.0,2.0,4.0.</x:v>
+        <x:v>List of fixed potential values, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to assign three potential values, enter 0.0,2.0,4.0.</x:v>
       </x:c>
       <x:c r="E9" s="61" t="n">
         <x:v>0</x:v>
@@ -1549,7 +1549,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field data, if IBFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field data when IBIFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E11" s="61" t="str">
         <x:v>linear</x:v>
@@ -1583,7 +1583,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D13" s="62" t="str">
-        <x:v>magnetic field value at x = 0 m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = 0 m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E13" s="61" t="n">
         <x:v>17.1</x:v>
@@ -1600,7 +1600,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D14" s="62" t="str">
-        <x:v>magnetic field value at x = L m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = L m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E14" s="61" t="n">
         <x:v>17.1</x:v>
@@ -1634,7 +1634,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D16" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field gradient data, if IALPHAB = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field-gradient data when IALPHAB = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E16" s="61" t="str">
         <x:v>linear</x:v>
@@ -1719,7 +1719,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D21" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the heat data, if IQFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the heat data when IQFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E21" s="61" t="str">
         <x:v>linear</x:v>
@@ -1787,7 +1787,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D25" s="62" t="str">
-        <x:v>heating start time. Recommended: add the time at with the heating starts also if the heat is from external file, IQFUN = -1 (requested for the correct evaluation of htc between fluid and solid)</x:v>
+        <x:v>Heating start time. Specify this time even when the heat is read from an external file (IQFUN = -1); it is required for the correct evaluation of the HTC between the fluid and the solid.</x:v>
       </x:c>
       <x:c r="E25" s="61" t="n">
         <x:v>610.01</x:v>
@@ -1872,7 +1872,7 @@
         <x:v>bool</x:v>
       </x:c>
       <x:c r="D30" s="62" t="str">
-        <x:v>Flag to decide if the current sharing temperature should be evaluated at each time steps or not (improve speed). Possible values: False = evaluate the current sharing temperature only at the initialization and at the end of the simulation; True = evaluate the current sharing temperature at each time steps (affects computaion time). Defaults to False.</x:v>
+        <x:v>Flag used to determine whether the current-sharing temperature is evaluated at every time step. Possible values: False = evaluate it only during initialization and at the end of the simulation; True = evaluate it at every time step (increases computation time). Defaults to False.</x:v>
       </x:c>
       <x:c r="E30" s="79" t="b">
         <x:v>1</x:v>
@@ -2018,7 +2018,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the operating current data, if IOP_MODE = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the operating-current data when IOP_MODE = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E5" s="61" t="str">
         <x:v>linear</x:v>
@@ -2041,7 +2041,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D6" s="62" t="str">
-        <x:v>Flag to allow user to specify the potential value in some axial location of the conductor. Possible values: 1 = user can assign the position and the value of the potential; 0 = user can not assign these values. Defaults to 0</x:v>
+        <x:v>Flag used to allow the user to specify potential values at selected axial locations of the conductor. Possible values: 1 = the user can assign the locations and potential values; 0 = the user cannot assign these values. Defaults to 0.</x:v>
       </x:c>
       <x:c r="E6" s="78" t="n">
         <x:v>1</x:v>
@@ -2087,7 +2087,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D8" s="62" t="str">
-        <x:v>List of axial coordinate at which assing the fix potential value, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if at z = 0.5m z = 1.0m and z = 1.5m user wants to fix the potential value, write 0.5,1.0,1.5.</x:v>
+        <x:v>List of axial coordinates at which the fixed potential values are assigned, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to fix the potential at z = 0.5 m, 1.0 m, and 1.5 m, enter 0.5,1.0,1.5.</x:v>
       </x:c>
       <x:c r="E8" s="61" t="n">
         <x:v>0</x:v>
@@ -2110,7 +2110,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D9" s="62" t="str">
-        <x:v>List of fix potential value the user wants to assig, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if user wants to assign three potential values, write: 0.0,2.0,4.0.</x:v>
+        <x:v>List of fixed potential values, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to assign three potential values, enter 0.0,2.0,4.0.</x:v>
       </x:c>
       <x:c r="E9" s="61" t="n">
         <x:v>0</x:v>
@@ -2156,7 +2156,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field data, if IBFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field data when IBIFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E11" s="61" t="str">
         <x:v>linear</x:v>
@@ -2202,7 +2202,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D13" s="62" t="str">
-        <x:v>magnetic field value at x = 0 m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = 0 m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E13" s="61" t="n">
         <x:v>17</x:v>
@@ -2225,7 +2225,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D14" s="62" t="str">
-        <x:v>magnetic field value at x = L m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = L m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E14" s="61" t="n">
         <x:v>17</x:v>
@@ -2271,7 +2271,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D16" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field gradient data, if IALPHAB = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field-gradient data when IALPHAB = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E16" s="61" t="str">
         <x:v>linear</x:v>
@@ -2317,7 +2317,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D18" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the heat data, if IQFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the heat data when IQFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E18" s="61" t="str">
         <x:v>linear</x:v>
@@ -2409,7 +2409,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D22" s="62" t="str">
-        <x:v>heating start time. Recommended: add the time at with the heating starts also if the heat is from external file, IQFUN = -1 (requested for the correct evaluation of htc between fluid and solid)</x:v>
+        <x:v>Heating start time. Specify this time even when the heat is read from an external file (IQFUN = -1); it is required for the correct evaluation of the HTC between the fluid and the solid.</x:v>
       </x:c>
       <x:c r="E22" s="61" t="n">
         <x:v>0</x:v>
@@ -2637,7 +2637,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the operating current data, if IOP_MODE = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the operating-current data when IOP_MODE = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E5" s="61" t="str">
         <x:v>linear</x:v>
@@ -2671,7 +2671,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D7" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field data, if IBFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field data when IBIFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E7" s="61" t="str">
         <x:v>linear</x:v>
@@ -2705,7 +2705,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D9" s="62" t="str">
-        <x:v>magnetic field value at x = 0 m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = 0 m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E9" s="61" t="n">
         <x:v>17</x:v>
@@ -2722,7 +2722,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D10" s="62" t="str">
-        <x:v>magnetic field value at x = L m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = L m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E10" s="61" t="n">
         <x:v>17</x:v>
@@ -2756,7 +2756,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D12" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field gradient data, if IALPHAB = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field-gradient data when IALPHAB = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E12" s="61" t="str">
         <x:v>linear</x:v>
@@ -2790,7 +2790,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D14" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the heat data, if IQFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the heat data when IQFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E14" s="61" t="str">
         <x:v>linear</x:v>
@@ -2858,7 +2858,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D18" s="62" t="str">
-        <x:v>heating start time. Recommended: add the time at with the heating starts also if the heat is from external file, IQFUN = -1 (requested for the correct evaluation of htc between fluid and solid)</x:v>
+        <x:v>Heating start time. Specify this time even when the heat is read from an external file (IQFUN = -1); it is required for the correct evaluation of the HTC between the fluid and the solid.</x:v>
       </x:c>
       <x:c r="E18" s="61" t="n">
         <x:v>0</x:v>
